--- a/src/attributions/attributions_ig_traj_394.xlsx
+++ b/src/attributions/attributions_ig_traj_394.xlsx
@@ -2140,61 +2140,61 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.08076942317994767</v>
+        <v>0.1387570036169907</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.01847096240799937</v>
+        <v>-0.02498449340499314</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.06767998576285246</v>
+        <v>-0.1030823743595191</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.04216054928418907</v>
+        <v>0.1700023273065119</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.01468455147315662</v>
+        <v>-0.02735857801171767</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.06672472609998353</v>
+        <v>-0.07457970269232427</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>5.708439885912414e-12</v>
+        <v>-2.558142639178416e-11</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -2203,40 +2203,40 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002520037062374271</v>
+        <v>0.01706111615645593</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.002112603545596681</v>
+        <v>0.009347031862759706</v>
       </c>
       <c r="Y4" t="n">
         <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB4" t="n">
         <v>-0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.01391400644292028</v>
+        <v>-0.06548754380717903</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.02957691879151703</v>
+        <v>-0.1046079467347704</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.001549212891400271</v>
+        <v>-0.08241309304028695</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>-0</v>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.01441368732102465</v>
+        <v>0.02153529010807928</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
@@ -2257,25 +2257,25 @@
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.01462919445918285</v>
+        <v>-0.03715731997875695</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.02106500077168694</v>
+        <v>-0.03848168757817726</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.09090677900953878</v>
+        <v>0.3890924011383775</v>
       </c>
       <c r="AV4" t="n">
         <v>-0</v>
@@ -2284,10 +2284,10 @@
         <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.01600966717597957</v>
+        <v>-0.06132339336605144</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.07567087386375836</v>
+        <v>-0.0351895046234973</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
@@ -2296,67 +2296,67 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.01608589070804325</v>
+        <v>-0.01107291029832763</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF4" t="n">
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.01700265041844347</v>
+        <v>-0.04024385683916955</v>
       </c>
       <c r="BH4" t="n">
-        <v>-0.007771802805500499</v>
+        <v>-0.0184610703376685</v>
       </c>
       <c r="BI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.03269204688543417</v>
+        <v>0.05262900604165596</v>
       </c>
       <c r="BN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
         <v>-0</v>
       </c>
       <c r="BP4" t="n">
-        <v>-0.003074087254476579</v>
+        <v>0.08481062041638451</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.01626849174701902</v>
+        <v>0.07760977542142686</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU4" t="n">
         <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.04560114269296734</v>
+        <v>0.1598831054758606</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
@@ -2365,148 +2365,148 @@
         <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.01756205628799199</v>
+        <v>-0.08259797227731101</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0.01446840571202998</v>
+        <v>-0.1058887146511702</v>
       </c>
       <c r="CA4" t="n">
         <v>-0</v>
       </c>
       <c r="CB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD4" t="n">
         <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.02074226007656471</v>
+        <v>-0.05474288575403815</v>
       </c>
       <c r="CF4" t="n">
         <v>0</v>
       </c>
       <c r="CG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.002043177636136521</v>
+        <v>0.003704661674378044</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.03853816540237043</v>
+        <v>0.07458817203732385</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK4" t="n">
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.003719433942601462</v>
+        <v>-0.1529851686049501</v>
       </c>
       <c r="CO4" t="n">
         <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.00697327253638651</v>
+        <v>0.1069343762396791</v>
       </c>
       <c r="CR4" t="n">
-        <v>-0.009020041102596753</v>
+        <v>0.05783731014403425</v>
       </c>
       <c r="CS4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.01569839733856047</v>
+        <v>-0.0594608485117137</v>
       </c>
       <c r="CX4" t="n">
         <v>-0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.005542299695693505</v>
+        <v>-0.01192300605142636</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.04065598502812606</v>
+        <v>0.06724411720598644</v>
       </c>
       <c r="DB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.01157535131479475</v>
+        <v>0.006242489097362424</v>
       </c>
       <c r="DG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.01934196304787508</v>
+        <v>-0.07389585178004736</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.05505241337042874</v>
+        <v>-0.01360590512804183</v>
       </c>
       <c r="DK4" t="n">
         <v>0</v>
       </c>
       <c r="DL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN4" t="n">
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.01245432214355841</v>
+        <v>-0.04038146107019872</v>
       </c>
       <c r="DP4" t="n">
         <v>0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.02006725362062987</v>
+        <v>0.05877979967028613</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.01423290602189675</v>
+        <v>0.1086601068533526</v>
       </c>
       <c r="DT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
@@ -2518,19 +2518,19 @@
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.003404167583787482</v>
+        <v>-0.009575795250474283</v>
       </c>
       <c r="DY4" t="n">
         <v>0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.00162617212841725</v>
+        <v>0.006031606511750003</v>
       </c>
       <c r="EB4" t="n">
-        <v>-0.03413847434947449</v>
+        <v>-0.08126959347573769</v>
       </c>
       <c r="EC4" t="n">
         <v>-0</v>
@@ -2542,10 +2542,10 @@
         <v>0</v>
       </c>
       <c r="EF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.007599755171492572</v>
+        <v>-0.05014652682547931</v>
       </c>
       <c r="EH4" t="n">
         <v>-0</v>
@@ -2554,52 +2554,52 @@
         <v>0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>-0.004739036904437425</v>
+        <v>-0.05298117823259583</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.01503981058642621</v>
+        <v>0.03554215801754798</v>
       </c>
       <c r="EL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.003912484757605518</v>
+        <v>0.03154082223808995</v>
       </c>
       <c r="EQ4" t="n">
         <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.01424284769046315</v>
+        <v>-0.05766857916611944</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.04022835499835994</v>
+        <v>0.04829236173470495</v>
       </c>
       <c r="EU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW4" t="n">
         <v>0</v>
       </c>
       <c r="EX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.01599478243518172</v>
+        <v>-0.06688223602522013</v>
       </c>
       <c r="EZ4" t="n">
         <v>-0</v>
@@ -2608,37 +2608,37 @@
         <v>0</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.003078302818425221</v>
+        <v>-0.01896920196947787</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.03722398791256894</v>
+        <v>0.05728196456214888</v>
       </c>
       <c r="FD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
         <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
         <v>0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.01743484543849065</v>
+        <v>-0.1096596172972644</v>
       </c>
       <c r="FI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ4" t="n">
         <v>-0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.01246135598973959</v>
+        <v>0.02922740426031701</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.00716781318314257</v>
+        <v>-0.04876755047591894</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
@@ -2647,25 +2647,25 @@
         <v>-0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
         <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.0002921100931353198</v>
+        <v>0.06088690880976404</v>
       </c>
       <c r="FR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>-0.007054767615090453</v>
+        <v>0.01346201044343565</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.03619073311025166</v>
+        <v>0.05757407774955149</v>
       </c>
       <c r="FV4" t="n">
         <v>-0</v>
@@ -2674,13 +2674,13 @@
         <v>-0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.01945625937887183</v>
+        <v>-0.006288282588492816</v>
       </c>
       <c r="GA4" t="n">
         <v>0</v>
@@ -2692,16 +2692,16 @@
         <v>0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0.01079207120096872</v>
+        <v>0.04307719355574974</v>
       </c>
       <c r="GE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="5">
@@ -2709,43 +2709,43 @@
         <v>-0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1925137838297053</v>
+        <v>0.228824220277128</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.08534506459253899</v>
+        <v>-0.1035991624611842</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0918120790461292</v>
+        <v>-0.03928094218756487</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H5" t="n">
         <v>-0</v>
       </c>
       <c r="I5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>-0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1039720456581782</v>
+        <v>0.1804132779232199</v>
       </c>
       <c r="L5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.02685712736805953</v>
+        <v>-0.04981009377602397</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.08519203771433986</v>
+        <v>-0.06038329113422317</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -2760,22 +2760,22 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.005781409945446294</v>
+        <v>0.006855502835622406</v>
       </c>
       <c r="U5" t="n">
         <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>8.8688244849843e-05</v>
+        <v>-0.00140632673583467</v>
       </c>
       <c r="W5" t="n">
-        <v>1.712564885282161e-11</v>
+        <v>-5.348741043009976e-13</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>-0</v>
@@ -2787,55 +2787,55 @@
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.07877656999528786</v>
+        <v>-0.0263627263609442</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.004563071840458834</v>
+        <v>-0.07499694786900579</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.0369639943061584</v>
+        <v>-0.08276082903566635</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.00695749810171758</v>
+        <v>0.1080420449894621</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.04441919066268623</v>
+        <v>-0.02868402634805199</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.08305545310066911</v>
+        <v>0.05125494484067072</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
         <v>0</v>
@@ -2844,22 +2844,22 @@
         <v>-0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.370759195985766</v>
+        <v>0.3125756729560583</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.01430438409576296</v>
+        <v>-0.1390308224186541</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.1213645949312456</v>
+        <v>-0.1591024926954763</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
@@ -2871,16 +2871,16 @@
         <v>-0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.0004980416170470086</v>
+        <v>-0.01507075617926543</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.03698053621462844</v>
+        <v>-0.005297202595235197</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.06028350271834866</v>
+        <v>-0.01022639824231629</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
@@ -2889,31 +2889,31 @@
         <v>-0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK5" t="n">
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.1174486281815664</v>
+        <v>-0.006988329243094641</v>
       </c>
       <c r="BN5" t="n">
         <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.04478800082791886</v>
+        <v>0.04727742547793481</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.1318413088399543</v>
+        <v>0.07587416605650818</v>
       </c>
       <c r="BQ5" t="n">
         <v>-0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2925,52 +2925,52 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.1822110570570007</v>
+        <v>0.2127830448662407</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.003185631590356411</v>
+        <v>-0.1120330324053744</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.01849783771665158</v>
+        <v>-0.02526776689698343</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
         <v>0</v>
       </c>
       <c r="CD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.05675669267101693</v>
+        <v>-0.1137821079276439</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.02230095409953892</v>
+        <v>0.08955827748085186</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.001175070211351701</v>
+        <v>0.0248869257127541</v>
       </c>
       <c r="CI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ5" t="n">
         <v>-0</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL5" t="n">
         <v>-0</v>
@@ -2979,16 +2979,16 @@
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.04372672021524558</v>
+        <v>-0.08744174370366417</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.05830111191623655</v>
+        <v>0.07602980130562148</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.1366926305044485</v>
+        <v>0.06648087371522343</v>
       </c>
       <c r="CR5" t="n">
         <v>0</v>
@@ -2997,25 +2997,25 @@
         <v>-0</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU5" t="n">
         <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.03913875059908033</v>
+        <v>-0.1190826683526444</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.04268251342068213</v>
+        <v>0.1037671623569342</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.02086608458524998</v>
+        <v>0.02845208197985794</v>
       </c>
       <c r="DA5" t="n">
         <v>0</v>
@@ -3033,22 +3033,22 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.001655348176029702</v>
+        <v>-0.005542753169524936</v>
       </c>
       <c r="DG5" t="n">
         <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.02306340463834056</v>
+        <v>0.02819831096480927</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.003627790129963488</v>
+        <v>-0.08821758820135331</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL5" t="n">
         <v>0</v>
@@ -3060,52 +3060,52 @@
         <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.07003386662760699</v>
+        <v>-0.06872111776782755</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0.02351677648364726</v>
+        <v>0.04731800366558982</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.001540481232191079</v>
+        <v>-0.02400581170086125</v>
       </c>
       <c r="DS5" t="n">
         <v>-0</v>
       </c>
       <c r="DT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.0262937360114307</v>
+        <v>0.06629510689339337</v>
       </c>
       <c r="DY5" t="n">
         <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.04277024896393954</v>
+        <v>0.02948374376917755</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.0230515720238223</v>
+        <v>-0.03462759787348877</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
         <v>-0</v>
@@ -3114,19 +3114,19 @@
         <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.03864272150095772</v>
+        <v>-0.06828138118766708</v>
       </c>
       <c r="EH5" t="n">
         <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.07112891367353338</v>
+        <v>0.09640686866089533</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.08053219928704609</v>
+        <v>0.03574506572790243</v>
       </c>
       <c r="EK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL5" t="n">
         <v>-0</v>
@@ -3141,22 +3141,22 @@
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.04501846675466722</v>
+        <v>-0.0604748732104792</v>
       </c>
       <c r="EQ5" t="n">
         <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.05663793337100684</v>
+        <v>0.06180723985325336</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.01126478869394736</v>
+        <v>-0.02916180896491667</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV5" t="n">
         <v>-0</v>
@@ -3165,46 +3165,46 @@
         <v>-0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.04442805820114921</v>
+        <v>-0.1258312851704646</v>
       </c>
       <c r="EZ5" t="n">
         <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.04212768186273488</v>
+        <v>0.105589972790594</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.01563562580298947</v>
+        <v>0.0154282581727809</v>
       </c>
       <c r="FC5" t="n">
         <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF5" t="n">
         <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.06282471186636412</v>
+        <v>-0.04525848759386286</v>
       </c>
       <c r="FI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>-0.04301221921953948</v>
+        <v>-0.04420840966997896</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.0019280692886305</v>
+        <v>0.02191797620127267</v>
       </c>
       <c r="FL5" t="n">
         <v>-0</v>
@@ -3216,22 +3216,22 @@
         <v>-0</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.043318710509792</v>
+        <v>0.01226760792889086</v>
       </c>
       <c r="FR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.03897791680113114</v>
+        <v>0.1248252155735617</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.05761517209657267</v>
+        <v>-0.06041516448337903</v>
       </c>
       <c r="FU5" t="n">
         <v>0</v>
@@ -3246,22 +3246,22 @@
         <v>0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.03412246080192088</v>
+        <v>-0.09578541207266493</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
-        <v>-0.01480787842605745</v>
+        <v>0.05948797599405316</v>
       </c>
       <c r="GC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
         <v>-0</v>
@@ -3275,22 +3275,22 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.02782393383268718</v>
+        <v>0.03712848433812847</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.01559542180892867</v>
+        <v>0.02142019269563711</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.009258751536564426</v>
+        <v>-0.01707081278205807</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -3302,25 +3302,25 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.008131481268280248</v>
+        <v>0.05373517676087597</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.01956125401453946</v>
+        <v>0.01229055443659268</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.01091372043595223</v>
+        <v>-0.01446307965817753</v>
       </c>
       <c r="P6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -3329,10 +3329,10 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0005966308510706949</v>
+        <v>-0.0004325828756043843</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3341,43 +3341,43 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.0001888760622963166</v>
+        <v>-0.002787034752975036</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.002962742986816485</v>
+        <v>-1.792013663250379e-06</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB6" t="n">
         <v>-0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.02109725440465995</v>
+        <v>-0.01635824424239507</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.02531265114089981</v>
+        <v>-0.06066115129117021</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.00246610636935063</v>
+        <v>-0.01679543374939272</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ6" t="n">
         <v>-0</v>
@@ -3386,7 +3386,7 @@
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.004510887188661666</v>
+        <v>0.01168301610637086</v>
       </c>
       <c r="AM6" t="n">
         <v>0</v>
@@ -3395,52 +3395,52 @@
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.01959965652028364</v>
+        <v>-0.01434411067500559</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.005882854579549997</v>
+        <v>-0.02529876832812857</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS6" t="n">
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.05412120741952653</v>
+        <v>0.09875596756461393</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW6" t="n">
         <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.009802111662536986</v>
+        <v>-0.01943522925225755</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.01076732077736483</v>
+        <v>-0.01838019328363848</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA6" t="n">
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.004315976217693894</v>
+        <v>-0.00487602600451125</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
@@ -3449,13 +3449,13 @@
         <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.01368576525200661</v>
+        <v>-0.007609525832982128</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.001366183993760958</v>
+        <v>0.002395115275741752</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
         <v>0</v>
@@ -3464,37 +3464,37 @@
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.0336910432878058</v>
+        <v>0.01866277747304215</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO6" t="n">
         <v>-0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.01439691459014573</v>
+        <v>0.04173358663986046</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.0118512319489197</v>
+        <v>0.03409152862583778</v>
       </c>
       <c r="BR6" t="n">
         <v>-0</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT6" t="n">
         <v>0</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.01694271412948513</v>
+        <v>0.04118488871094406</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
@@ -3503,13 +3503,13 @@
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.01283477272274623</v>
+        <v>0.001325857268277679</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.01662696976433324</v>
+        <v>-0.03708044231635034</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB6" t="n">
         <v>0</v>
@@ -3521,76 +3521,76 @@
         <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.001693972286678692</v>
+        <v>-0.01047707067974978</v>
       </c>
       <c r="CF6" t="n">
         <v>0</v>
       </c>
       <c r="CG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.0003712928735546207</v>
+        <v>-0.002108178234733249</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.006451436150486278</v>
+        <v>0.02405936811295317</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL6" t="n">
         <v>-0</v>
       </c>
       <c r="CM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.0006644369398006079</v>
+        <v>-0.03508550171491758</v>
       </c>
       <c r="CO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.001053101298587852</v>
+        <v>0.04502679388384824</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.01282934674502711</v>
+        <v>0.02789475244635544</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT6" t="n">
         <v>-0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
         <v>0</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.003344289639930693</v>
+        <v>-0.01331958609046578</v>
       </c>
       <c r="CX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.001157522804953674</v>
+        <v>-0.004270787276275972</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.006106140133160662</v>
+        <v>0.02121913319221934</v>
       </c>
       <c r="DB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC6" t="n">
         <v>0</v>
@@ -3602,19 +3602,19 @@
         <v>-0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.001852835318017518</v>
+        <v>-0.01617594033639813</v>
       </c>
       <c r="DG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>-0.0001895047228193837</v>
+        <v>-0.001064567760628056</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.01871159047405375</v>
+        <v>-0.003523175290866117</v>
       </c>
       <c r="DK6" t="n">
         <v>0</v>
@@ -3623,25 +3623,25 @@
         <v>-0</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN6" t="n">
         <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.001820474599737121</v>
+        <v>-0.0153737443441057</v>
       </c>
       <c r="DP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.01535141098325061</v>
+        <v>7.409133693750962e-05</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.001889069572495153</v>
+        <v>0.03213523252670954</v>
       </c>
       <c r="DT6" t="n">
         <v>-0</v>
@@ -3653,10 +3653,10 @@
         <v>-0</v>
       </c>
       <c r="DW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.01223162396320741</v>
+        <v>-0.01295577334282887</v>
       </c>
       <c r="DY6" t="n">
         <v>0</v>
@@ -3665,94 +3665,94 @@
         <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.009191403740202475</v>
+        <v>0.002814190894353654</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0.001833120063116223</v>
+        <v>0.02446225345983214</v>
       </c>
       <c r="EC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
         <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.006357255892505897</v>
+        <v>-0.01080889328031065</v>
       </c>
       <c r="EH6" t="n">
         <v>-0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.001392742350043461</v>
+        <v>-0.02199237795393105</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.003510129990783777</v>
+        <v>0.003103374969377853</v>
       </c>
       <c r="EL6" t="n">
         <v>-0</v>
       </c>
       <c r="EM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN6" t="n">
         <v>-0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>3.729942837441042e-05</v>
+        <v>0.0007600325855249119</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.01578290485131721</v>
+        <v>-0.001565374007990659</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.03356015294431564</v>
+        <v>0.01499122191866191</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV6" t="n">
         <v>0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
         <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.004309386553961092</v>
+        <v>-0.01705192624588623</v>
       </c>
       <c r="EZ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.000228584618482213</v>
+        <v>-0.00970881426106953</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.009681713409627075</v>
+        <v>0.0153849863928878</v>
       </c>
       <c r="FD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE6" t="n">
         <v>-0</v>
@@ -3761,22 +3761,22 @@
         <v>-0</v>
       </c>
       <c r="FG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.008446368275227802</v>
+        <v>-0.01971668677198928</v>
       </c>
       <c r="FI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ6" t="n">
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.01479862643705192</v>
+        <v>0.01594839736016723</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.0202884689087738</v>
+        <v>0.005371425375104234</v>
       </c>
       <c r="FM6" t="n">
         <v>0</v>
@@ -3785,13 +3785,13 @@
         <v>-0</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.007393320064506325</v>
+        <v>0.01510448415170241</v>
       </c>
       <c r="FR6" t="n">
         <v>-0</v>
@@ -3800,10 +3800,10 @@
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>-0.002895829147449729</v>
+        <v>0.00155113318371415</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.004140814156674915</v>
+        <v>-0.03461950676010011</v>
       </c>
       <c r="FV6" t="n">
         <v>-0</v>
@@ -3812,13 +3812,13 @@
         <v>-0</v>
       </c>
       <c r="FX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.02229866830504462</v>
+        <v>0.01130239746978062</v>
       </c>
       <c r="GA6" t="n">
         <v>0</v>
@@ -3830,13 +3830,13 @@
         <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0.004937106194178441</v>
+        <v>0.0172265317772104</v>
       </c>
       <c r="GE6" t="n">
         <v>0</v>
       </c>
       <c r="GF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG6" t="n">
         <v>0</v>
@@ -3847,7 +3847,7 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1157973378073804</v>
+        <v>0.05982785543491352</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -3856,25 +3856,25 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.01888611850555134</v>
+        <v>-0.02816361253010265</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H7" t="n">
         <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.02107324558172558</v>
+        <v>-0.007355081799822986</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.04880471926000608</v>
+        <v>0.07687090466918672</v>
       </c>
       <c r="L7" t="n">
         <v>-0</v>
@@ -3883,7 +3883,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0644177797388101</v>
+        <v>-0.02748800305992127</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3892,16 +3892,16 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.02251793420936797</v>
+        <v>-0.005274831205656832</v>
       </c>
       <c r="S7" t="n">
         <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.005874062873725826</v>
+        <v>-0.002589470224559138</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
@@ -3910,34 +3910,34 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.002447361927208395</v>
+        <v>-0.005782485380555162</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0003725336374915654</v>
+        <v>0.000563189299046905</v>
       </c>
       <c r="AB7" t="n">
         <v>-0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.04149708601296588</v>
+        <v>-0.01490321844704932</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.02607616003242012</v>
+        <v>-0.02038181863313916</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -3946,16 +3946,16 @@
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.01488846753321022</v>
+        <v>-0.0001845680344107254</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.03138981973372649</v>
+        <v>0.02593522760776453</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
@@ -3964,37 +3964,37 @@
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.02727370259129835</v>
+        <v>-0.007144888605449513</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.01731448137987254</v>
+        <v>-0.005603466366752727</v>
       </c>
       <c r="AT7" t="n">
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.1935376323867256</v>
+        <v>0.09992165269972296</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.07277057282857734</v>
+        <v>-0.01821091549883491</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
@@ -4003,13 +4003,13 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0.0003824305947670898</v>
+        <v>0.01052069548223344</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.01097397833739699</v>
+        <v>-0.003512588147706564</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
@@ -4018,79 +4018,79 @@
         <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.04120615729825915</v>
+        <v>-0.01460257223943284</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.009173598055853506</v>
+        <v>0.005367835116004059</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.02190361948079069</v>
+        <v>0.01414217347826378</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.08372236780627075</v>
+        <v>0.0391841818385693</v>
       </c>
       <c r="BQ7" t="n">
         <v>-0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.02808049399066705</v>
+        <v>0.012705586960818</v>
       </c>
       <c r="BU7" t="n">
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.09919377248250179</v>
+        <v>0.05286826990227807</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.01006090570066358</v>
+        <v>-0.02219741449291546</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB7" t="n">
         <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.008949243702275249</v>
+        <v>-0.01763293443434796</v>
       </c>
       <c r="CD7" t="n">
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.02398855891557518</v>
+        <v>-0.02361719501555963</v>
       </c>
       <c r="CF7" t="n">
         <v>-0</v>
@@ -4099,10 +4099,10 @@
         <v>-0</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.0009641349049909969</v>
+        <v>0.009180244697177334</v>
       </c>
       <c r="CI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ7" t="n">
         <v>-0</v>
@@ -4111,25 +4111,25 @@
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.02884687910318126</v>
+        <v>0.01213761279826337</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.02397463096183432</v>
+        <v>-0.04458796260768575</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
         <v>-0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.01982257958279183</v>
+        <v>0.007458809614198586</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4138,13 +4138,13 @@
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>-0.01044412825071706</v>
+        <v>0.01820300189962124</v>
       </c>
       <c r="CV7" t="n">
         <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.01923108182190582</v>
+        <v>-0.02453129573205228</v>
       </c>
       <c r="CX7" t="n">
         <v>0</v>
@@ -4153,34 +4153,34 @@
         <v>0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.006148750870387569</v>
+        <v>0.005053074899488049</v>
       </c>
       <c r="DA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB7" t="n">
         <v>0</v>
       </c>
       <c r="DC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.02858891844373446</v>
+        <v>0.01126313486678568</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.0768473471704548</v>
+        <v>-0.01782194752844915</v>
       </c>
       <c r="DG7" t="n">
         <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.02968946841663445</v>
+        <v>-0.01144192126884171</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
@@ -4189,97 +4189,97 @@
         <v>0</v>
       </c>
       <c r="DL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM7" t="n">
-        <v>-0.0079470943350913</v>
+        <v>-0.006475289075396498</v>
       </c>
       <c r="DN7" t="n">
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.0007070776768410674</v>
+        <v>-0.01892147647554972</v>
       </c>
       <c r="DP7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.00538740716006825</v>
+        <v>0.009724185501635589</v>
       </c>
       <c r="DS7" t="n">
         <v>-0</v>
       </c>
       <c r="DT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU7" t="n">
         <v>-0</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.0001369393628435813</v>
+        <v>-0.02803207509805088</v>
       </c>
       <c r="DW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.001981749515028409</v>
+        <v>0.008899702453635276</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
         <v>-0</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.01827239438641064</v>
+        <v>0.006884073404754506</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>-0.009604118742497947</v>
+        <v>-0.007481074817924746</v>
       </c>
       <c r="EF7" t="n">
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.002900217694050681</v>
+        <v>-0.01970714586460603</v>
       </c>
       <c r="EH7" t="n">
         <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.03048563630266237</v>
+        <v>0.000567752314464368</v>
       </c>
       <c r="EK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
         <v>0</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.0308367706929612</v>
+        <v>0.004705272602067906</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.03727883303050775</v>
+        <v>-0.003636732632245878</v>
       </c>
       <c r="EQ7" t="n">
         <v>-0</v>
@@ -4288,25 +4288,25 @@
         <v>-0</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.004776090605190121</v>
+        <v>0.005535712157619527</v>
       </c>
       <c r="ET7" t="n">
         <v>-0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.01268053725079802</v>
+        <v>0.006963329807203627</v>
       </c>
       <c r="EX7" t="n">
         <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.03048360336731324</v>
+        <v>-0.02833336052521404</v>
       </c>
       <c r="EZ7" t="n">
         <v>-0</v>
@@ -4315,7 +4315,7 @@
         <v>-0</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.007177352467209592</v>
+        <v>0.002015671429800959</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
@@ -4327,40 +4327,40 @@
         <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.01650902544005424</v>
+        <v>0.01196682263095781</v>
       </c>
       <c r="FG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.03177935392518871</v>
+        <v>-0.01758889262835519</v>
       </c>
       <c r="FI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.02351258617591647</v>
+        <v>0.007664045436050225</v>
       </c>
       <c r="FL7" t="n">
         <v>0</v>
       </c>
       <c r="FM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.01294999322205836</v>
+        <v>0.04094948033255865</v>
       </c>
       <c r="FP7" t="n">
         <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.05199328894180477</v>
+        <v>0.008480929448869443</v>
       </c>
       <c r="FR7" t="n">
         <v>-0</v>
@@ -4369,7 +4369,7 @@
         <v>-0</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.01184258597869111</v>
+        <v>-0.01847161718205543</v>
       </c>
       <c r="FU7" t="n">
         <v>0</v>
@@ -4378,19 +4378,19 @@
         <v>-0</v>
       </c>
       <c r="FW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.0003741397621200349</v>
+        <v>0.001996867527515103</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.03909111012020897</v>
+        <v>-0.01224090228397323</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
         <v>-0</v>
@@ -4399,16 +4399,16 @@
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.03558599850766829</v>
+        <v>0.0009783301352714281</v>
       </c>
     </row>
     <row r="8">
@@ -4985,22 +4985,22 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3106437831270257</v>
+        <v>0.2038531997270258</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1496018185409515</v>
+        <v>-0.08113918749686591</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.03374901671874667</v>
+        <v>-0.05489576244484037</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H9" t="n">
         <v>-0</v>
@@ -5012,97 +5012,97 @@
         <v>-0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1697126951937322</v>
+        <v>0.1782581336494417</v>
       </c>
       <c r="L9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1423169249253365</v>
+        <v>-0.1185918047347259</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.09410128015314211</v>
+        <v>-0.117983752164156</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.04453996599713637</v>
+        <v>0.03566064447060675</v>
       </c>
       <c r="U9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0.005697712575746993</v>
+        <v>-0.006219793312972568</v>
       </c>
       <c r="W9" t="n">
-        <v>0.003550425223815959</v>
+        <v>-0.01831588859725281</v>
       </c>
       <c r="X9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
         <v>-0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.1436082497318555</v>
+        <v>-0.006528752163506183</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.05435999256701774</v>
+        <v>-0.08194888300662988</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.03515494326920635</v>
+        <v>-0.1236625666963575</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>-0.007756782793840201</v>
+        <v>0.1630972527079614</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.0316841434212757</v>
+        <v>-0.0633047089646243</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.1229906483654108</v>
+        <v>0.06479708654263655</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
@@ -5114,25 +5114,25 @@
         <v>-0</v>
       </c>
       <c r="AS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
         <v>-0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.4719931033194477</v>
+        <v>0.2420950180208511</v>
       </c>
       <c r="AV9" t="n">
         <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.03751369256533733</v>
+        <v>-0.01696531514722461</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.2111707188669428</v>
+        <v>-0.2995448284892708</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
@@ -5147,16 +5147,16 @@
         <v>-0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.003993062569399903</v>
+        <v>-0.03350105533591202</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.05873728247999443</v>
+        <v>-0.0106665594939784</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.1237338661837435</v>
+        <v>0.008694142987897845</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
         <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
@@ -5174,19 +5174,19 @@
         <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.2021824751866237</v>
+        <v>0.01290175618916034</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.01229024564659119</v>
+        <v>0.009419064622503746</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.1672406240285256</v>
+        <v>0.01328439115848721</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
         <v>-0</v>
@@ -5201,52 +5201,52 @@
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.2492858087171118</v>
+        <v>0.2235756458345536</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.02143861452588544</v>
+        <v>-0.1500872879102026</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.05020676034669944</v>
+        <v>-0.07709098332976579</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB9" t="n">
         <v>0</v>
       </c>
       <c r="CC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD9" t="n">
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.06796379875061495</v>
+        <v>-0.0750462387141007</v>
       </c>
       <c r="CF9" t="n">
         <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.002395838879714606</v>
+        <v>0.0771536934274374</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.01609241205007882</v>
+        <v>0.02861724924973107</v>
       </c>
       <c r="CI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL9" t="n">
         <v>-0</v>
@@ -5255,25 +5255,25 @@
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.1100282079297027</v>
+        <v>-0.07658161740827928</v>
       </c>
       <c r="CO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.1461013875502917</v>
+        <v>0.2382367961343912</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.1107085597182291</v>
+        <v>0.1367989907477695</v>
       </c>
       <c r="CR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS9" t="n">
         <v>-0</v>
       </c>
       <c r="CT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU9" t="n">
         <v>-0</v>
@@ -5282,25 +5282,25 @@
         <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.03723055642946148</v>
+        <v>-0.05663466385616859</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.02706039880496515</v>
+        <v>0.08838840673546074</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.002575053257487002</v>
+        <v>0.04824457525109795</v>
       </c>
       <c r="DA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD9" t="n">
         <v>0</v>
@@ -5309,22 +5309,22 @@
         <v>-0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.01786790571581448</v>
+        <v>-0.00567819335093815</v>
       </c>
       <c r="DG9" t="n">
         <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.01666092615580402</v>
+        <v>0.01473842601341886</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.03702723470786631</v>
+        <v>-0.03584635869727257</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL9" t="n">
         <v>0</v>
@@ -5336,52 +5336,52 @@
         <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.06706473905452226</v>
+        <v>-0.08436221946597044</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0.05417780427934395</v>
+        <v>0.06801955337732601</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.0001292172065608839</v>
+        <v>0.01725904189853034</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.03412264745845685</v>
+        <v>0.01457589973827719</v>
       </c>
       <c r="DY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>-0.04244409367875661</v>
+        <v>0.04002734596508113</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.028084615555417</v>
+        <v>-0.03658383956314525</v>
       </c>
       <c r="EB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC9" t="n">
         <v>0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
         <v>-0</v>
@@ -5390,22 +5390,22 @@
         <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.00104551353622646</v>
+        <v>0.01014923604507556</v>
       </c>
       <c r="EH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.06333572788325965</v>
+        <v>0.04756256518909269</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.04966400099544546</v>
+        <v>0.03739855184523346</v>
       </c>
       <c r="EK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
         <v>-0</v>
@@ -5414,25 +5414,25 @@
         <v>-0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.07630707054726414</v>
+        <v>-0.07647855227598555</v>
       </c>
       <c r="EQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER9" t="n">
-        <v>-0.05927988856981358</v>
+        <v>-0.07031774589585255</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.01244967879751701</v>
+        <v>0.004447900649768763</v>
       </c>
       <c r="ET9" t="n">
         <v>-0</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
         <v>0</v>
@@ -5444,106 +5444,106 @@
         <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.05108775312552004</v>
+        <v>-0.07462165679557337</v>
       </c>
       <c r="EZ9" t="n">
         <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.01316886067597326</v>
+        <v>0.1016023389025633</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.01737067343135156</v>
+        <v>0.02855862061646099</v>
       </c>
       <c r="FC9" t="n">
         <v>-0</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF9" t="n">
         <v>-0</v>
       </c>
       <c r="FG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.06351992522688722</v>
+        <v>-0.02396138918935608</v>
       </c>
       <c r="FI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.04079100799245006</v>
+        <v>0.008882533734044419</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.00227220744707745</v>
+        <v>-0.0279436194657608</v>
       </c>
       <c r="FL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.06349191649528482</v>
+        <v>0.01827712906460486</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>-0.06039463508063075</v>
+        <v>0.103417232304178</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.1055411958067576</v>
+        <v>-0.1234867615180661</v>
       </c>
       <c r="FU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX9" t="n">
         <v>0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.03878665617750221</v>
+        <v>-0.01181343096368102</v>
       </c>
       <c r="GA9" t="n">
         <v>-0</v>
       </c>
       <c r="GB9" t="n">
-        <v>-0.07562386639912644</v>
+        <v>0.02808224088694637</v>
       </c>
       <c r="GC9" t="n">
         <v>0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE9" t="n">
         <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
         <v>0</v>
@@ -5554,16 +5554,16 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4402908514670354</v>
+        <v>0.2037832830014901</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1776899168732325</v>
+        <v>-0.2888141335960017</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1418458309131852</v>
+        <v>-0.07491221661823454</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -5572,7 +5572,7 @@
         <v>-0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.006966383837568238</v>
+        <v>0.02447036570075511</v>
       </c>
       <c r="I10" t="n">
         <v>-0</v>
@@ -5581,16 +5581,16 @@
         <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2490331763040262</v>
+        <v>0.174705239876572</v>
       </c>
       <c r="L10" t="n">
         <v>-0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.148039526802476</v>
+        <v>-0.3095760244180281</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2338881086436558</v>
+        <v>-0.1492657441614744</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -5599,115 +5599,115 @@
         <v>-0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0006259025869889794</v>
+        <v>-0.001105663249885597</v>
       </c>
       <c r="R10" t="n">
         <v>-0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1065809864257045</v>
+        <v>0.0722678589137136</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.0268071246896393</v>
+        <v>-0.05047717173778517</v>
       </c>
       <c r="W10" t="n">
-        <v>0.001552151021050291</v>
+        <v>-0.1020631528213641</v>
       </c>
       <c r="X10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.0008924633462729152</v>
+        <v>0.003881745697124137</v>
       </c>
       <c r="AA10" t="n">
         <v>-0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.09702848550428238</v>
+        <v>-0.1283148604504059</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.08233241587958723</v>
+        <v>-0.03017024628606194</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.04257525955572922</v>
+        <v>-0.08905555866648555</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.01401107604170282</v>
+        <v>0.03311207736722214</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.02131876206002882</v>
+        <v>0.1263495863312806</v>
       </c>
       <c r="AM10" t="n">
         <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.07242933967075005</v>
+        <v>-0.07630702988220006</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.1017482921480195</v>
+        <v>0.05147781854651416</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.01617926028399346</v>
+        <v>0.01198593984402357</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT10" t="n">
         <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.6401103171666822</v>
+        <v>0.2893094015918879</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.002108271263173253</v>
+        <v>-0.1217417004546559</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.2245702194138643</v>
+        <v>-0.354150924984085</v>
       </c>
       <c r="AY10" t="n">
         <v>-0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.07107810982269756</v>
+        <v>-0.08724159206880358</v>
       </c>
       <c r="BB10" t="n">
         <v>-0</v>
@@ -5716,16 +5716,16 @@
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.00785688324501623</v>
+        <v>-0.05986605946397448</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0.06010580422804935</v>
+        <v>-0.0650980753169651</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.2662472994592956</v>
+        <v>-0.03574943126090678</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
@@ -5734,34 +5734,34 @@
         <v>-0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.002449231348911655</v>
+        <v>-0.02866176140733907</v>
       </c>
       <c r="BK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL10" t="n">
         <v>-0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.2429090222732718</v>
+        <v>0.04861284346879469</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.1456087020890262</v>
+        <v>0.1466919665859817</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.1699019906205022</v>
+        <v>-0.01976120739596995</v>
       </c>
       <c r="BQ10" t="n">
         <v>-0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.04320480267832511</v>
+        <v>0.0324023610015878</v>
       </c>
       <c r="BT10" t="n">
         <v>-0</v>
@@ -5770,25 +5770,25 @@
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.3162437509486433</v>
+        <v>0.2456945935037586</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.0400318113890943</v>
+        <v>-0.2864576996366371</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.05188468513082019</v>
+        <v>-0.2112666216355801</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.007521382952760131</v>
+        <v>-0.1054686411933939</v>
       </c>
       <c r="CC10" t="n">
         <v>-0</v>
@@ -5797,16 +5797,16 @@
         <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.101160596047404</v>
+        <v>-0.05499714777011778</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.0229675376556018</v>
+        <v>0.1906744014472945</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.004657245054452024</v>
+        <v>0.04406873866729712</v>
       </c>
       <c r="CI10" t="n">
         <v>-0</v>
@@ -5815,7 +5815,7 @@
         <v>-0</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.004038552324802264</v>
+        <v>-0.04448576870258352</v>
       </c>
       <c r="CL10" t="n">
         <v>-0</v>
@@ -5824,43 +5824,43 @@
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.1356251083885716</v>
+        <v>-0.02289425753294078</v>
       </c>
       <c r="CO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>-0.1641882851359851</v>
+        <v>0.2595797865408556</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.05490725202692203</v>
+        <v>0.3637670111067784</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS10" t="n">
         <v>-0</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.06718983377328348</v>
+        <v>0.0585429995435945</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.06636422345437699</v>
+        <v>-0.04862481109404838</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.05763117494988689</v>
+        <v>0.2132609369384624</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.0005202180727150902</v>
+        <v>0.05361507268586196</v>
       </c>
       <c r="DA10" t="n">
         <v>0</v>
@@ -5869,25 +5869,25 @@
         <v>0</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.003444438859980974</v>
+        <v>-0.02805899517790003</v>
       </c>
       <c r="DD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.07123888000159292</v>
+        <v>-0.04807838238533471</v>
       </c>
       <c r="DG10" t="n">
         <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.0374631971371692</v>
+        <v>0.07770019251880458</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.001851989678323579</v>
+        <v>0.002172116493734509</v>
       </c>
       <c r="DJ10" t="n">
         <v>0</v>
@@ -5896,25 +5896,25 @@
         <v>-0</v>
       </c>
       <c r="DL10" t="n">
-        <v>-0.001310824437900616</v>
+        <v>-0.07590514941435968</v>
       </c>
       <c r="DM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.1066586137105585</v>
+        <v>-0.02427778843604934</v>
       </c>
       <c r="DP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>-0.03923077863142565</v>
+        <v>0.1615132988856327</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.03561540871482522</v>
+        <v>-0.08232503438719706</v>
       </c>
       <c r="DS10" t="n">
         <v>-0</v>
@@ -5923,25 +5923,25 @@
         <v>-0</v>
       </c>
       <c r="DU10" t="n">
-        <v>-0.02522504243065432</v>
+        <v>0.104558980426973</v>
       </c>
       <c r="DV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0.02519298664173803</v>
+        <v>0.06271611286078257</v>
       </c>
       <c r="DY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>-0.04589391014469666</v>
+        <v>0.0451318436718809</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.07160045068613582</v>
+        <v>-0.1437483411068835</v>
       </c>
       <c r="EB10" t="n">
         <v>0</v>
@@ -5950,25 +5950,25 @@
         <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0.02118818310187182</v>
+        <v>0.1739612174830064</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.04794935135944808</v>
+        <v>0.0379358855243038</v>
       </c>
       <c r="EH10" t="n">
         <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.07367924319550254</v>
+        <v>0.1246479604653597</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.04090626549340704</v>
+        <v>0.06757237840747127</v>
       </c>
       <c r="EK10" t="n">
         <v>-0</v>
@@ -5977,7 +5977,7 @@
         <v>-0</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.04009067728754524</v>
+        <v>-0.05033098625422448</v>
       </c>
       <c r="EN10" t="n">
         <v>-0</v>
@@ -5986,70 +5986,70 @@
         <v>0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.1079617439587324</v>
+        <v>-0.02757688383288115</v>
       </c>
       <c r="EQ10" t="n">
         <v>-0</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.1037272876147865</v>
+        <v>0.2030011510997251</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.04483390238004744</v>
+        <v>-0.06937361838338883</v>
       </c>
       <c r="ET10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV10" t="n">
-        <v>-0.00136057393496394</v>
+        <v>-0.0009428889590980693</v>
       </c>
       <c r="EW10" t="n">
         <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.07592910406450924</v>
+        <v>-0.06742579030054373</v>
       </c>
       <c r="EZ10" t="n">
         <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.04356421108616246</v>
+        <v>0.246767694188142</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.02225964380285048</v>
+        <v>0.05602622781645105</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.003030290770007936</v>
+        <v>-0.03497920720315621</v>
       </c>
       <c r="FF10" t="n">
         <v>-0</v>
       </c>
       <c r="FG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.06987662061938599</v>
+        <v>-0.03163541344862434</v>
       </c>
       <c r="FI10" t="n">
         <v>0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>-0.05421930011404287</v>
+        <v>-0.08311249805496355</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.03335611530846368</v>
+        <v>0.05539711950421286</v>
       </c>
       <c r="FL10" t="n">
         <v>-0</v>
@@ -6058,52 +6058,52 @@
         <v>-0</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.007098462823188424</v>
+        <v>-0.02796401927501889</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.1219724884991377</v>
+        <v>0.05478819605519924</v>
       </c>
       <c r="FR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS10" t="n">
-        <v>-0.08357035109170222</v>
+        <v>0.1081896727516915</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.09229050393218217</v>
+        <v>-0.1990645357384621</v>
       </c>
       <c r="FU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV10" t="n">
         <v>-0</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.008932623429281633</v>
+        <v>-0.1058639318717313</v>
       </c>
       <c r="FX10" t="n">
         <v>0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.1172272258305028</v>
+        <v>-0.02064031808132022</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>-0.03033963152094096</v>
+        <v>0.09914100015616503</v>
       </c>
       <c r="GC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD10" t="n">
         <v>-0</v>
@@ -6112,7 +6112,7 @@
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.03123071478992191</v>
+        <v>-0.06565948080125297</v>
       </c>
       <c r="GG10" t="n">
         <v>-0</v>
@@ -6120,28 +6120,28 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1865634434479534</v>
+        <v>0.3591296481222924</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1302053806074242</v>
+        <v>-0.05106011268492122</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.08240439811231196</v>
+        <v>-0.187656555530653</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1088697099824431</v>
+        <v>0.4377175183951577</v>
       </c>
       <c r="L11" t="n">
         <v>-0</v>
@@ -6159,13 +6159,13 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1281176697042004</v>
+        <v>-0.1293232921374403</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.07876987932786376</v>
+        <v>-0.1443597019812578</v>
       </c>
       <c r="P11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -6177,46 +6177,46 @@
         <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.03304338114315511</v>
+        <v>0.07716060458123238</v>
       </c>
       <c r="U11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.006650847669861908</v>
+        <v>-0.0796230169657947</v>
       </c>
       <c r="X11" t="n">
-        <v>0.03076074914782129</v>
+        <v>0.01819838696483514</v>
       </c>
       <c r="Y11" t="n">
         <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB11" t="n">
         <v>-0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.04379694355965294</v>
+        <v>-0.01530240948405742</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.01475748682426094</v>
+        <v>-0.2506541964051529</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.02516536047205831</v>
+        <v>0.03418912367227398</v>
       </c>
       <c r="AH11" t="n">
         <v>-0</v>
@@ -6231,22 +6231,22 @@
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.03857611322968073</v>
+        <v>0.09201908051935868</v>
       </c>
       <c r="AM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.02760179976334685</v>
+        <v>-0.07985548849950699</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.0193334364507083</v>
+        <v>-0.03951063040167963</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
         <v>-0</v>
@@ -6255,91 +6255,91 @@
         <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.2119165070281292</v>
+        <v>0.5857517245665375</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW11" t="n">
         <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>-0.02572358315253303</v>
+        <v>-0.2752603484228326</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0.01592252274512002</v>
+        <v>-0.04888862301609824</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC11" t="n">
         <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.03866057386769809</v>
+        <v>-0.06040421458708998</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.09153474870413542</v>
+        <v>-0.0335871965211462</v>
       </c>
       <c r="BH11" t="n">
-        <v>-0.05024011274409517</v>
+        <v>-0.08654955577533426</v>
       </c>
       <c r="BI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
         <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.1076782255551417</v>
+        <v>0.1569303085930682</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO11" t="n">
         <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.06667108456247167</v>
+        <v>0.1560699282740714</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.03409840142123192</v>
+        <v>0.09139915285120435</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU11" t="n">
         <v>-0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.1011734890604092</v>
+        <v>0.3735571744274589</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
@@ -6348,67 +6348,67 @@
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>-0.01977159078658653</v>
+        <v>-0.1115786911199154</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.02779504962385125</v>
+        <v>-0.03823369720241609</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
       </c>
       <c r="CB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.03559337887299662</v>
+        <v>-0.1279890876039655</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
         <v>-0</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.01822059129608778</v>
+        <v>0.02256971587740098</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.01929302833236883</v>
+        <v>0.07399927710890281</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM11" t="n">
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.0445878841842258</v>
+        <v>-0.2636117363127156</v>
       </c>
       <c r="CO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP11" t="n">
         <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.03298268144222425</v>
+        <v>0.121344608887043</v>
       </c>
       <c r="CR11" t="n">
-        <v>-0.02508261477963157</v>
+        <v>0.01742693454961776</v>
       </c>
       <c r="CS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT11" t="n">
         <v>-0</v>
@@ -6417,28 +6417,28 @@
         <v>0</v>
       </c>
       <c r="CV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.017985031504329</v>
+        <v>-0.1097705722462472</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.01874719641363956</v>
+        <v>-0.003075520229841572</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.02236965421006079</v>
+        <v>0.07508946835003825</v>
       </c>
       <c r="DB11" t="n">
         <v>0</v>
       </c>
       <c r="DC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD11" t="n">
         <v>0</v>
@@ -6447,7 +6447,7 @@
         <v>-0</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.05143239313786468</v>
+        <v>-0.09197592202918278</v>
       </c>
       <c r="DG11" t="n">
         <v>-0</v>
@@ -6456,37 +6456,37 @@
         <v>-0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.0159314567753884</v>
+        <v>-0.1490227464455757</v>
       </c>
       <c r="DJ11" t="n">
-        <v>-0.0002423546146745756</v>
+        <v>-0.01367423371157464</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
       </c>
       <c r="DL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN11" t="n">
         <v>-0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.04216957147418027</v>
+        <v>-0.07376251070379498</v>
       </c>
       <c r="DP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.01458771520107713</v>
+        <v>-0.02793933427835928</v>
       </c>
       <c r="DS11" t="n">
-        <v>-0.04208701483568133</v>
+        <v>-0.02729498101605462</v>
       </c>
       <c r="DT11" t="n">
         <v>-0</v>
@@ -6498,10 +6498,10 @@
         <v>-0</v>
       </c>
       <c r="DW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>-0.003986210686452977</v>
+        <v>0.08537736869893352</v>
       </c>
       <c r="DY11" t="n">
         <v>0</v>
@@ -6510,124 +6510,124 @@
         <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.04198985929512244</v>
+        <v>-0.01582887716102315</v>
       </c>
       <c r="EB11" t="n">
-        <v>-0.02542270482494236</v>
+        <v>0.03855357360429381</v>
       </c>
       <c r="EC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
         <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.005027047569210839</v>
+        <v>0.01386504161939162</v>
       </c>
       <c r="EH11" t="n">
         <v>-0</v>
       </c>
       <c r="EI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.01873699305996717</v>
+        <v>-0.05401528258263141</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.004154785308562642</v>
+        <v>0.07571180723998581</v>
       </c>
       <c r="EL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN11" t="n">
         <v>-0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.01728467213138319</v>
+        <v>0.0126241370280083</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.002320854417367035</v>
+        <v>-0.1386827953618545</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.03525829029920941</v>
+        <v>0.04822835541919987</v>
       </c>
       <c r="EU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW11" t="n">
         <v>0</v>
       </c>
       <c r="EX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.01461014540536462</v>
+        <v>-0.142189826522389</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA11" t="n">
         <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.01594024991814146</v>
+        <v>-0.01502083522447728</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.0289982909196963</v>
+        <v>0.05422238257152306</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.03070063399817069</v>
+        <v>-0.1372314897122613</v>
       </c>
       <c r="FI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ11" t="n">
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.03780213641873379</v>
+        <v>0.1616519437113771</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.01770195720889136</v>
+        <v>0.0264106093264029</v>
       </c>
       <c r="FM11" t="n">
         <v>0</v>
       </c>
       <c r="FN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO11" t="n">
         <v>0</v>
@@ -6636,34 +6636,34 @@
         <v>0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.000452934342167223</v>
+        <v>0.07825576716876249</v>
       </c>
       <c r="FR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS11" t="n">
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>-0.01935817327100704</v>
+        <v>-0.1346880245873687</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.01246006239132413</v>
+        <v>-0.007745106156269917</v>
       </c>
       <c r="FV11" t="n">
         <v>0</v>
       </c>
       <c r="FW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.05802236918049801</v>
+        <v>-0.07389228301723756</v>
       </c>
       <c r="GA11" t="n">
         <v>0</v>
@@ -6675,7 +6675,7 @@
         <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0.02594940694075738</v>
+        <v>0.080784303138208</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
@@ -6692,22 +6692,22 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.2585153132086625</v>
+        <v>0.3950328023694134</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1686446863551635</v>
+        <v>-0.2087978866281697</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.02017214448635723</v>
+        <v>-0.05296587565049665</v>
       </c>
       <c r="F12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H12" t="n">
         <v>-0</v>
@@ -6716,28 +6716,28 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1563564221590762</v>
+        <v>0.3845330001377895</v>
       </c>
       <c r="L12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1437769102282347</v>
+        <v>-0.2248418078269236</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.06638234473752368</v>
+        <v>-0.09948823012429342</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -6746,19 +6746,19 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.06570230656072314</v>
+        <v>0.05600321341120023</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>0.008407401189072418</v>
+        <v>-0.02724196989825272</v>
       </c>
       <c r="W12" t="n">
-        <v>0.04471970760466819</v>
+        <v>-0.06208188159067839</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
@@ -6770,73 +6770,73 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.124459273960484</v>
+        <v>-0.06877830711963676</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.02086072358761885</v>
+        <v>-0.1188429949968559</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.02639332139670282</v>
+        <v>-0.1062929554607908</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.002559026151670163</v>
+        <v>0.1340193935562568</v>
       </c>
       <c r="AM12" t="n">
         <v>-0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.02529102811409886</v>
+        <v>-0.09545708585495148</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.07618914747940428</v>
+        <v>0.03126652364227383</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.3419070177365711</v>
+        <v>0.3094568808012116</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.005273432373482418</v>
+        <v>-0.1161855399624546</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.124256827913943</v>
+        <v>-0.205463667455526</v>
       </c>
       <c r="AY12" t="n">
         <v>-0</v>
@@ -6851,19 +6851,19 @@
         <v>-0</v>
       </c>
       <c r="BC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>-0.01030745468903699</v>
+        <v>0.009206620301579514</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.07915704481120342</v>
+        <v>-0.04232729668611915</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.1191054579585076</v>
+        <v>-0.002223484794021725</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
@@ -6872,7 +6872,7 @@
         <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
@@ -6881,22 +6881,22 @@
         <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.1158812285994092</v>
+        <v>-0.002111483849140773</v>
       </c>
       <c r="BN12" t="n">
         <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.02521354130257183</v>
+        <v>0.03110105393542522</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.1136421157503044</v>
+        <v>0.09127456602519418</v>
       </c>
       <c r="BQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
         <v>-0</v>
@@ -6908,49 +6908,49 @@
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.189070896259754</v>
+        <v>0.2348663823613087</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.007879261781835387</v>
+        <v>-0.1176925063423981</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.06922827212524421</v>
+        <v>-0.07475053757216388</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD12" t="n">
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.05226841224733999</v>
+        <v>-0.1310066929873942</v>
       </c>
       <c r="CF12" t="n">
         <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.006285900333130461</v>
+        <v>0.1193329669473275</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.01458688918768843</v>
+        <v>0.02552225133173575</v>
       </c>
       <c r="CI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK12" t="n">
         <v>0</v>
@@ -6962,19 +6962,19 @@
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.07041460897981097</v>
+        <v>-0.1131350449251929</v>
       </c>
       <c r="CO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.07583204960531706</v>
+        <v>0.2463945747785149</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.07019359876893472</v>
+        <v>0.07277803394449223</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
         <v>-0</v>
@@ -6989,25 +6989,25 @@
         <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.02541963845771949</v>
+        <v>-0.1183408312950071</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.02274550385454497</v>
+        <v>0.1334407512667896</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.0100365903669998</v>
+        <v>0.02834792867344735</v>
       </c>
       <c r="DA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD12" t="n">
         <v>0</v>
@@ -7016,22 +7016,22 @@
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.04389298225528473</v>
+        <v>-0.0928076063411767</v>
       </c>
       <c r="DG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.01716590832923312</v>
+        <v>0.01422384190555152</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.03692698110862352</v>
+        <v>-0.07073310872495486</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL12" t="n">
         <v>0</v>
@@ -7043,130 +7043,130 @@
         <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.04174413105859101</v>
+        <v>-0.08096211196197442</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0.01128278476884811</v>
+        <v>0.0720250469466146</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.04954121363105128</v>
+        <v>-0.001088526139908489</v>
       </c>
       <c r="DS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT12" t="n">
         <v>-0</v>
       </c>
       <c r="DU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.0514452093391151</v>
+        <v>0.06509568213677727</v>
       </c>
       <c r="DY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.02075242958094164</v>
+        <v>-0.03333305812797443</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.03125575549540042</v>
+        <v>-0.006701963909182778</v>
       </c>
       <c r="EB12" t="n">
         <v>0</v>
       </c>
       <c r="EC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
         <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.005678476387738914</v>
+        <v>-0.07279431232800324</v>
       </c>
       <c r="EH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.05321134446500952</v>
+        <v>0.09768036902130622</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.05355431272106312</v>
+        <v>0.05240636822610768</v>
       </c>
       <c r="EK12" t="n">
         <v>0</v>
       </c>
       <c r="EL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
         <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.04933644385127156</v>
+        <v>-0.0488207178853442</v>
       </c>
       <c r="EQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.03554958189861267</v>
+        <v>0.07648794465388374</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.03717662215899917</v>
+        <v>-0.0339198312081035</v>
       </c>
       <c r="ET12" t="n">
         <v>-0</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW12" t="n">
         <v>-0</v>
       </c>
       <c r="EX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.03729433951483967</v>
+        <v>-0.1400457624128451</v>
       </c>
       <c r="EZ12" t="n">
         <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.0236981962296835</v>
+        <v>0.1379859051104171</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.003043856951867318</v>
+        <v>0.01204151180321365</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
         <v>0</v>
@@ -7178,16 +7178,16 @@
         <v>-0</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.0522424468499029</v>
+        <v>-0.07150365790348963</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.02444072011443786</v>
+        <v>0.08118035364152086</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.03887936883982937</v>
+        <v>0.0003705793036517412</v>
       </c>
       <c r="FL12" t="n">
         <v>-0</v>
@@ -7196,28 +7196,28 @@
         <v>0</v>
       </c>
       <c r="FN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.04154018757349524</v>
+        <v>-0.008180237267442337</v>
       </c>
       <c r="FR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS12" t="n">
-        <v>-0.01839396973323576</v>
+        <v>0.1140546928992156</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.05438533229967223</v>
+        <v>-0.03808796196529279</v>
       </c>
       <c r="FU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV12" t="n">
         <v>-0</v>
@@ -7229,31 +7229,31 @@
         <v>0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.009332734428241906</v>
+        <v>-0.1079580283973764</v>
       </c>
       <c r="GA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.06913356310096716</v>
+        <v>0.07289938346297914</v>
       </c>
       <c r="GC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -7261,19 +7261,19 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5185063179863727</v>
+        <v>0.4073228090042268</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1179979846420672</v>
+        <v>0.04320054583626062</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4376010567670041</v>
+        <v>-0.3717729146860736</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -7288,25 +7288,25 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3856824358488302</v>
+        <v>0.57335375008319</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.09370407366375788</v>
+        <v>-0.0245608522699627</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.410393103553941</v>
+        <v>-0.3553263371970249</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -7315,25 +7315,25 @@
         <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.06820004108577755</v>
+        <v>0.1456345125166129</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.01530539943999252</v>
+        <v>-0.2264868952760413</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.0130274978593091</v>
+        <v>-0.05200875330886534</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -7342,19 +7342,19 @@
         <v>-0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.06713986913547565</v>
+        <v>-0.02190309275146219</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.03962432792171616</v>
+        <v>-0.417141041081785</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.04421853005414508</v>
+        <v>-0.2514647934263119</v>
       </c>
       <c r="AH13" t="n">
         <v>-0</v>
@@ -7369,7 +7369,7 @@
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.07633332945673493</v>
+        <v>0.1020678561665656</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
@@ -7378,13 +7378,13 @@
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.004872177228289499</v>
+        <v>-0.02553582052107546</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.07313004676063878</v>
+        <v>-0.1684260851964395</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
         <v>-0</v>
@@ -7393,10 +7393,10 @@
         <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.4269903245182938</v>
+        <v>0.8873330947869275</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
@@ -7405,16 +7405,16 @@
         <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.01770353952600189</v>
+        <v>-0.1775837659606637</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.1932952309689211</v>
+        <v>-0.1759708162771872</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
         <v>0</v>
@@ -7423,49 +7423,49 @@
         <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.1291667249990226</v>
+        <v>-0.169205700083209</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF13" t="n">
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.1286876607711013</v>
+        <v>-0.1505615279922543</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.1521274950037579</v>
+        <v>-0.196556250856916</v>
       </c>
       <c r="BI13" t="n">
         <v>0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.1542809442765107</v>
+        <v>0.1239133116992787</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO13" t="n">
         <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.0750799339653711</v>
+        <v>0.1213684441463595</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.0277011756899567</v>
+        <v>-0.00511410393909395</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
         <v>0</v>
@@ -7474,76 +7474,76 @@
         <v>-0</v>
       </c>
       <c r="BU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.2263450917345012</v>
+        <v>0.4473331287753896</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX13" t="n">
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.04870400958920722</v>
+        <v>-0.215245459654778</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0.1303070872179324</v>
+        <v>-0.2843435265409654</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
       </c>
       <c r="CB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC13" t="n">
         <v>0</v>
       </c>
       <c r="CD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.09784281174618389</v>
+        <v>-0.1592345933454791</v>
       </c>
       <c r="CF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.00765751443833173</v>
+        <v>0.06097506017167273</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.09737834580871796</v>
+        <v>0.150337191130392</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
         <v>0</v>
       </c>
       <c r="CL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM13" t="n">
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.09014309949054794</v>
+        <v>-0.4211496138385225</v>
       </c>
       <c r="CO13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.0276355863351632</v>
+        <v>0.4720913305247045</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0.0006680196033950707</v>
+        <v>0.3401136123282189</v>
       </c>
       <c r="CS13" t="n">
         <v>-0</v>
@@ -7555,52 +7555,52 @@
         <v>-0</v>
       </c>
       <c r="CV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.07159357109089486</v>
+        <v>-0.1461100619129677</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.005891994711372056</v>
+        <v>0.02410375438756536</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.101092451870107</v>
+        <v>0.1193970299986466</v>
       </c>
       <c r="DB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC13" t="n">
         <v>-0</v>
       </c>
       <c r="DD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.07281881168860514</v>
+        <v>0.01046160444105882</v>
       </c>
       <c r="DG13" t="n">
         <v>0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.02450556154972473</v>
+        <v>-0.1366126670185251</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.01652226634082684</v>
+        <v>-0.001189539794212826</v>
       </c>
       <c r="DK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL13" t="n">
         <v>0</v>
@@ -7609,28 +7609,28 @@
         <v>0</v>
       </c>
       <c r="DN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.05717563368490503</v>
+        <v>0.003048456632361646</v>
       </c>
       <c r="DP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.02683868619840318</v>
+        <v>0.01543602242598683</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.009113176576573474</v>
+        <v>0.09005984084382285</v>
       </c>
       <c r="DT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV13" t="n">
         <v>0</v>
@@ -7639,22 +7639,22 @@
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.007952112733939209</v>
+        <v>0.1285360711117423</v>
       </c>
       <c r="DY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ13" t="n">
         <v>-0</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.00279448395870382</v>
+        <v>-0.03897891658409752</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.03410432812806338</v>
+        <v>0.07763175463550363</v>
       </c>
       <c r="EC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED13" t="n">
         <v>-0</v>
@@ -7666,34 +7666,34 @@
         <v>0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.03838704059535658</v>
+        <v>-0.04573933008737394</v>
       </c>
       <c r="EH13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.01835908158064451</v>
+        <v>-0.04609593626186081</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.08839811074440988</v>
+        <v>0.006518757808765893</v>
       </c>
       <c r="EL13" t="n">
         <v>-0</v>
       </c>
       <c r="EM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.0160716103308243</v>
+        <v>0.003570266133969546</v>
       </c>
       <c r="EQ13" t="n">
         <v>0</v>
@@ -7702,13 +7702,13 @@
         <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.01270540219610088</v>
+        <v>-0.02655048689554648</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.08677842422700745</v>
+        <v>0.1351815441970087</v>
       </c>
       <c r="EU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV13" t="n">
         <v>0</v>
@@ -7717,55 +7717,55 @@
         <v>-0</v>
       </c>
       <c r="EX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.06550756107412127</v>
+        <v>-0.1816737107857216</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA13" t="n">
         <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.003267952884683173</v>
+        <v>0.01384370491690126</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.09917313933793175</v>
+        <v>0.1322540154563119</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
         <v>0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG13" t="n">
         <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.0580137063140208</v>
+        <v>-0.192356945297178</v>
       </c>
       <c r="FI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ13" t="n">
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.007837599278915556</v>
+        <v>0.08880709481807642</v>
       </c>
       <c r="FL13" t="n">
-        <v>-0.05997968942058924</v>
+        <v>-0.05213789194286881</v>
       </c>
       <c r="FM13" t="n">
         <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
         <v>0</v>
@@ -7774,46 +7774,46 @@
         <v>0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.01262190898943434</v>
+        <v>0.06783526535576137</v>
       </c>
       <c r="FR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS13" t="n">
         <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.06056099862594497</v>
+        <v>0.08144449096385885</v>
       </c>
       <c r="FU13" t="n">
-        <v>-0.01232908799872844</v>
+        <v>-0.0332284412542726</v>
       </c>
       <c r="FV13" t="n">
         <v>-0</v>
       </c>
       <c r="FW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.02939909396928639</v>
+        <v>-0.04579181760740431</v>
       </c>
       <c r="GA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB13" t="n">
         <v>-0</v>
       </c>
       <c r="GC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0.04213593414578445</v>
+        <v>0.06290531820365147</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
@@ -7822,7 +7822,7 @@
         <v>-0</v>
       </c>
       <c r="GG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -7830,16 +7830,16 @@
         <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>0.5286229261194823</v>
+        <v>0.3158699107385374</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1682933753576391</v>
+        <v>-0.2091816824148929</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1480622399467619</v>
+        <v>-0.07296488742654306</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -7851,22 +7851,22 @@
         <v>-0</v>
       </c>
       <c r="I14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3210510663346797</v>
+        <v>0.3032209168562981</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1335369656452065</v>
+        <v>-0.238231551039344</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1316001884228508</v>
+        <v>-0.1751844613428093</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -7881,73 +7881,73 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1117279816552704</v>
+        <v>0.05799578147800542</v>
       </c>
       <c r="U14" t="n">
         <v>-0</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.02158566312028126</v>
+        <v>-0.04487026274576126</v>
       </c>
       <c r="W14" t="n">
-        <v>0.04833083859174277</v>
+        <v>-0.09307546798500087</v>
       </c>
       <c r="X14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>-0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.1046445436161811</v>
+        <v>0.02423116851649304</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.001436641937306982</v>
+        <v>-0.2131858562059053</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.004468306275816971</v>
+        <v>-0.1480064633480956</v>
       </c>
       <c r="AG14" t="n">
         <v>-0</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.01237921660874817</v>
+        <v>0.178125578188068</v>
       </c>
       <c r="AM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0.06953290459935094</v>
+        <v>-0.1184384663811728</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.08713374000156353</v>
+        <v>0.07385823547939044</v>
       </c>
       <c r="AP14" t="n">
         <v>0</v>
@@ -7962,79 +7962,79 @@
         <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.4215941120183702</v>
+        <v>0.389419172301979</v>
       </c>
       <c r="AV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.04964009408416269</v>
+        <v>-0.03212489805571409</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.06017346637853012</v>
+        <v>-0.3397454728965129</v>
       </c>
       <c r="AY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
         <v>-0</v>
       </c>
       <c r="BC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.02561790094416077</v>
+        <v>-0.01899038371414473</v>
       </c>
       <c r="BE14" t="n">
         <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>-0.09028068057331227</v>
+        <v>-0.06587328429601701</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.1991636031635254</v>
+        <v>0.07870527054459246</v>
       </c>
       <c r="BH14" t="n">
         <v>0</v>
       </c>
       <c r="BI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL14" t="n">
         <v>-0</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.1142891431536983</v>
+        <v>0.08500700001551872</v>
       </c>
       <c r="BN14" t="n">
         <v>-0</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.04587954234544138</v>
+        <v>0.028303443934695</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.1382088625069808</v>
+        <v>0.1402401492981124</v>
       </c>
       <c r="BQ14" t="n">
         <v>-0</v>
       </c>
       <c r="BR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS14" t="n">
         <v>-0</v>
@@ -8043,46 +8043,46 @@
         <v>-0</v>
       </c>
       <c r="BU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.2035575119718927</v>
+        <v>0.312404905154684</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.05509007064449815</v>
+        <v>-0.1357883951668966</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.022568866130664</v>
+        <v>-0.1183647899151353</v>
       </c>
       <c r="BZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA14" t="n">
         <v>-0</v>
       </c>
       <c r="CB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE14" t="n">
-        <v>-0.111813394843235</v>
+        <v>-0.1052702491756498</v>
       </c>
       <c r="CF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.01286188181493637</v>
+        <v>0.1108884852665053</v>
       </c>
       <c r="CH14" t="n">
-        <v>-0.01466756692226102</v>
+        <v>0.07218845797355354</v>
       </c>
       <c r="CI14" t="n">
         <v>-0</v>
@@ -8100,16 +8100,16 @@
         <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>-0.01167192036233329</v>
+        <v>-0.2331600958324831</v>
       </c>
       <c r="CO14" t="n">
         <v>-0</v>
       </c>
       <c r="CP14" t="n">
-        <v>-0.1003361007193509</v>
+        <v>0.2803232682732829</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.08523324662377142</v>
+        <v>0.1534350449978161</v>
       </c>
       <c r="CR14" t="n">
         <v>0</v>
@@ -8121,22 +8121,22 @@
         <v>-0</v>
       </c>
       <c r="CU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV14" t="n">
         <v>0</v>
       </c>
       <c r="CW14" t="n">
-        <v>-0.0897242764322768</v>
+        <v>-0.0820918754183622</v>
       </c>
       <c r="CX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.03302946616672613</v>
+        <v>0.1327258434369921</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-0.01722760092760546</v>
+        <v>0.08550454093164439</v>
       </c>
       <c r="DA14" t="n">
         <v>0</v>
@@ -8154,22 +8154,22 @@
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.003922458990247836</v>
+        <v>0.0004907938981227895</v>
       </c>
       <c r="DG14" t="n">
         <v>0</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.02030898642563894</v>
+        <v>0.01207645304313646</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.03519079441912639</v>
+        <v>-0.05648732279938776</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL14" t="n">
         <v>0</v>
@@ -8178,46 +8178,46 @@
         <v>0</v>
       </c>
       <c r="DN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>-0.04240361614842474</v>
+        <v>-0.1531636227629085</v>
       </c>
       <c r="DP14" t="n">
         <v>0</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.0621974110656051</v>
+        <v>-0.08882863677197381</v>
       </c>
       <c r="DR14" t="n">
-        <v>-0.0605255985000634</v>
+        <v>0.02661243513167274</v>
       </c>
       <c r="DS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT14" t="n">
         <v>-0</v>
       </c>
       <c r="DU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.03429717346658236</v>
+        <v>0.06514200108733545</v>
       </c>
       <c r="DY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ14" t="n">
-        <v>-0.002620446999818886</v>
+        <v>0.01428056574934007</v>
       </c>
       <c r="EA14" t="n">
-        <v>-0.08001545178529612</v>
+        <v>-0.1825299100342282</v>
       </c>
       <c r="EB14" t="n">
         <v>0</v>
@@ -8229,31 +8229,31 @@
         <v>0</v>
       </c>
       <c r="EE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG14" t="n">
-        <v>-0.09381341385750964</v>
+        <v>0.02198426846830494</v>
       </c>
       <c r="EH14" t="n">
         <v>0</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.03520125713244327</v>
+        <v>0.06244448253725335</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.07892704430982778</v>
+        <v>0.1034512014595454</v>
       </c>
       <c r="EK14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL14" t="n">
         <v>-0</v>
       </c>
       <c r="EM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN14" t="n">
         <v>-0</v>
@@ -8262,22 +8262,22 @@
         <v>0</v>
       </c>
       <c r="EP14" t="n">
-        <v>-0.06522627786196403</v>
+        <v>-0.05476204558060692</v>
       </c>
       <c r="EQ14" t="n">
         <v>0</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.02782078297904888</v>
+        <v>0.09078102826152033</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.01848593951006508</v>
+        <v>-0.07862688726569114</v>
       </c>
       <c r="ET14" t="n">
         <v>-0</v>
       </c>
       <c r="EU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV14" t="n">
         <v>0</v>
@@ -8286,73 +8286,73 @@
         <v>-0</v>
       </c>
       <c r="EX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY14" t="n">
-        <v>-0.09125827171909386</v>
+        <v>-0.1073073052711562</v>
       </c>
       <c r="EZ14" t="n">
         <v>-0</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.02283194429682905</v>
+        <v>0.1364412393038581</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.00987534587507934</v>
+        <v>0.0639890089759077</v>
       </c>
       <c r="FC14" t="n">
         <v>-0</v>
       </c>
       <c r="FD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE14" t="n">
         <v>0</v>
       </c>
       <c r="FF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH14" t="n">
-        <v>-0.0003180006781998393</v>
+        <v>0.005188697294808698</v>
       </c>
       <c r="FI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.06929151923482957</v>
+        <v>0.05296033607590241</v>
       </c>
       <c r="FK14" t="n">
-        <v>-0.08317110490858716</v>
+        <v>-0.01805545655418085</v>
       </c>
       <c r="FL14" t="n">
         <v>-0</v>
       </c>
       <c r="FM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO14" t="n">
         <v>0</v>
       </c>
       <c r="FP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>-0.008043162849473234</v>
+        <v>-0.004468880321969567</v>
       </c>
       <c r="FR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS14" t="n">
-        <v>-0.01642182428702299</v>
+        <v>0.07017537465539062</v>
       </c>
       <c r="FT14" t="n">
-        <v>-0.01429941892978378</v>
+        <v>-0.05596880545724875</v>
       </c>
       <c r="FU14" t="n">
         <v>-0</v>
@@ -8367,28 +8367,28 @@
         <v>0</v>
       </c>
       <c r="FY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.003505795873084772</v>
+        <v>-0.07757578989667949</v>
       </c>
       <c r="GA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB14" t="n">
-        <v>-0.06301702227592892</v>
+        <v>0.06356820805133331</v>
       </c>
       <c r="GC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG14" t="n">
         <v>-0</v>
@@ -8399,25 +8399,25 @@
         <v>-0</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.4564427839986571</v>
+        <v>-0.912736327151595</v>
       </c>
       <c r="C15" t="n">
         <v>-0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2645937004266292</v>
+        <v>0.276657939749587</v>
       </c>
       <c r="E15" t="n">
-        <v>0.05029196273180118</v>
+        <v>0.2131894304489016</v>
       </c>
       <c r="F15" t="n">
         <v>-0</v>
       </c>
       <c r="G15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>-0</v>
@@ -8426,43 +8426,43 @@
         <v>-0</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.3584621162462475</v>
+        <v>-0.796815906828906</v>
       </c>
       <c r="L15" t="n">
         <v>-0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3413410734431294</v>
+        <v>0.5482628141424475</v>
       </c>
       <c r="N15" t="n">
-        <v>0.05356714178850103</v>
+        <v>0.3571246172803763</v>
       </c>
       <c r="O15" t="n">
         <v>-0</v>
       </c>
       <c r="P15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>-0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.09614237776760634</v>
+        <v>-0.1037776246509489</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0.02824106467058407</v>
+        <v>0.07799695513659675</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.03924704271959094</v>
+        <v>-0.07829441995908046</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -8477,55 +8477,55 @@
         <v>-0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.1554327962074961</v>
+        <v>-0.06423400387823448</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0.003509899388694672</v>
+        <v>0.2864202063256174</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.01627363113032116</v>
+        <v>0.1136150783865677</v>
       </c>
       <c r="AG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>-0.03942215819081901</v>
+        <v>-0.4150014238202005</v>
       </c>
       <c r="AM15" t="n">
         <v>-0</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.05458761859278729</v>
+        <v>0.05244879658387949</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.006740524950795296</v>
+        <v>-0.3403655421146489</v>
       </c>
       <c r="AP15" t="n">
         <v>-0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
         <v>-0</v>
@@ -8534,16 +8534,16 @@
         <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>-0.2868105116609692</v>
+        <v>-0.634104113682101</v>
       </c>
       <c r="AV15" t="n">
         <v>-0</v>
       </c>
       <c r="AW15" t="n">
-        <v>-0.04567846155363928</v>
+        <v>0.09072542175975624</v>
       </c>
       <c r="AX15" t="n">
-        <v>-0.09678492282679307</v>
+        <v>0.2307521382570777</v>
       </c>
       <c r="AY15" t="n">
         <v>-0</v>
@@ -8555,31 +8555,31 @@
         <v>-0</v>
       </c>
       <c r="BB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
         <v>-0</v>
       </c>
       <c r="BD15" t="n">
-        <v>-0.060994002809046</v>
+        <v>0.05632031651349917</v>
       </c>
       <c r="BE15" t="n">
         <v>-0</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.1260205841323776</v>
+        <v>0.1681556469146647</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.3161785072602838</v>
+        <v>0.29833682654079</v>
       </c>
       <c r="BH15" t="n">
         <v>-0</v>
       </c>
       <c r="BI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK15" t="n">
         <v>-0</v>
@@ -8588,43 +8588,43 @@
         <v>0</v>
       </c>
       <c r="BM15" t="n">
-        <v>-0.02946675256962603</v>
+        <v>0.09283064879464462</v>
       </c>
       <c r="BN15" t="n">
         <v>0</v>
       </c>
       <c r="BO15" t="n">
-        <v>-0.04744744563050609</v>
+        <v>0.05669709403714238</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.01114303634050386</v>
+        <v>-0.00132070803679419</v>
       </c>
       <c r="BQ15" t="n">
         <v>0</v>
       </c>
       <c r="BR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU15" t="n">
         <v>0</v>
       </c>
       <c r="BV15" t="n">
-        <v>-0.1671870063711133</v>
+        <v>-0.5637401558266546</v>
       </c>
       <c r="BW15" t="n">
         <v>-0</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.06180267852582325</v>
+        <v>0.08645903138760314</v>
       </c>
       <c r="BY15" t="n">
-        <v>-0.08762867698990112</v>
+        <v>-0.01487060842618445</v>
       </c>
       <c r="BZ15" t="n">
         <v>-0</v>
@@ -8633,7 +8633,7 @@
         <v>0</v>
       </c>
       <c r="CB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC15" t="n">
         <v>-0</v>
@@ -8642,25 +8642,25 @@
         <v>0</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.102260595208331</v>
+        <v>0.3544411211071155</v>
       </c>
       <c r="CF15" t="n">
         <v>0</v>
       </c>
       <c r="CG15" t="n">
-        <v>-0.03668932714914622</v>
+        <v>-0.07078005141549859</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.06530475914507647</v>
+        <v>-0.02404325415407578</v>
       </c>
       <c r="CI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL15" t="n">
         <v>-0</v>
@@ -8669,19 +8669,19 @@
         <v>-0</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.005882245127220766</v>
+        <v>0.3190424401503327</v>
       </c>
       <c r="CO15" t="n">
         <v>0</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.04151398224568447</v>
+        <v>-0.1861428216689582</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.045201717457455</v>
+        <v>-0.3519891067140911</v>
       </c>
       <c r="CR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS15" t="n">
         <v>0</v>
@@ -8696,70 +8696,70 @@
         <v>-0</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.100421316766799</v>
+        <v>0.3412268856503627</v>
       </c>
       <c r="CX15" t="n">
         <v>-0</v>
       </c>
       <c r="CY15" t="n">
-        <v>-0.04622192058905903</v>
+        <v>-0.09493680664728187</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.04626496791398203</v>
+        <v>-0.05521438516684662</v>
       </c>
       <c r="DA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.08466932568737566</v>
+        <v>0.06186529567255992</v>
       </c>
       <c r="DG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH15" t="n">
-        <v>-0.02203101960767359</v>
+        <v>-0.01387244115832995</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.0004070333634122106</v>
+        <v>-0.00489891354893553</v>
       </c>
       <c r="DJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL15" t="n">
         <v>-0</v>
       </c>
       <c r="DM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN15" t="n">
         <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.07590698066888663</v>
+        <v>0.2343111342440873</v>
       </c>
       <c r="DP15" t="n">
         <v>0</v>
       </c>
       <c r="DQ15" t="n">
-        <v>-0.05312886466523319</v>
+        <v>0.02202330301963566</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.1096160086175421</v>
+        <v>-0.03959429573535491</v>
       </c>
       <c r="DS15" t="n">
         <v>-0</v>
@@ -8768,28 +8768,28 @@
         <v>0</v>
       </c>
       <c r="DU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV15" t="n">
         <v>-0</v>
       </c>
       <c r="DW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>-0.0492540127398517</v>
+        <v>-0.01951536392339258</v>
       </c>
       <c r="DY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0.09409950056447747</v>
+        <v>0.01485168319442403</v>
       </c>
       <c r="EA15" t="n">
-        <v>-0.06995481535679039</v>
+        <v>-0.05222393062196732</v>
       </c>
       <c r="EB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC15" t="n">
         <v>0</v>
@@ -8804,16 +8804,16 @@
         <v>0</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.05753397383782762</v>
+        <v>0.3017252770537278</v>
       </c>
       <c r="EH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI15" t="n">
-        <v>-0.02927969396526028</v>
+        <v>-0.06390782580217065</v>
       </c>
       <c r="EJ15" t="n">
-        <v>-0.02902700927530125</v>
+        <v>0.01142035694251024</v>
       </c>
       <c r="EK15" t="n">
         <v>0</v>
@@ -8822,79 +8822,79 @@
         <v>0</v>
       </c>
       <c r="EM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN15" t="n">
         <v>-0</v>
       </c>
       <c r="EO15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.09213268950902886</v>
+        <v>0.288804690490574</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.06094283278573027</v>
+        <v>-0.09356541237891038</v>
       </c>
       <c r="ES15" t="n">
-        <v>-0.05721127681160396</v>
+        <v>-0.1363201360235206</v>
       </c>
       <c r="ET15" t="n">
         <v>0</v>
       </c>
       <c r="EU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX15" t="n">
         <v>0</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.1215199366423891</v>
+        <v>0.4110215312147606</v>
       </c>
       <c r="EZ15" t="n">
         <v>0</v>
       </c>
       <c r="FA15" t="n">
-        <v>-0.05932624761504114</v>
+        <v>-0.07644842157276061</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.03902312133530724</v>
+        <v>-0.02821111364277752</v>
       </c>
       <c r="FC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG15" t="n">
         <v>0</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.03150407724905779</v>
+        <v>0.1802705484399746</v>
       </c>
       <c r="FI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ15" t="n">
-        <v>-0.06332466723590513</v>
+        <v>-0.09602228883389877</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.03453736482448729</v>
+        <v>0.06101317500817288</v>
       </c>
       <c r="FL15" t="n">
         <v>0</v>
@@ -8906,61 +8906,61 @@
         <v>-0</v>
       </c>
       <c r="FO15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP15" t="n">
         <v>0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.01096262480569038</v>
+        <v>0.03767897024941547</v>
       </c>
       <c r="FR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.06327563022043114</v>
+        <v>-0.1779649678504809</v>
       </c>
       <c r="FT15" t="n">
-        <v>-0.02816561991569894</v>
+        <v>-0.01975649860619454</v>
       </c>
       <c r="FU15" t="n">
         <v>0</v>
       </c>
       <c r="FV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX15" t="n">
         <v>-0</v>
       </c>
       <c r="FY15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.07351233589732836</v>
+        <v>0.2168129317972439</v>
       </c>
       <c r="GA15" t="n">
         <v>-0</v>
       </c>
       <c r="GB15" t="n">
-        <v>0.119375171760277</v>
+        <v>0.04428488457401013</v>
       </c>
       <c r="GC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE15" t="n">
         <v>0</v>
       </c>
       <c r="GF15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
   </sheetData>
